--- a/templates/oefen/oefen_geologie_template.xlsx
+++ b/templates/oefen/oefen_geologie_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15195" uniqueCount="2546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15192" uniqueCount="2546">
   <si>
     <t>identificatie</t>
   </si>
@@ -7628,25 +7628,25 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-02-10 16:32:23.896997</t>
+    <t>2026-03-31 16:51:51.468547</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.2.3</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>9.4.3</t>
+    <t>10.1.0</t>
   </si>
   <si>
     <t>schema-version</t>
   </si>
   <si>
-    <t>5.9.0</t>
+    <t>5.10.0</t>
   </si>
   <si>
     <t>mode</t>
@@ -55558,7 +55558,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BG6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54.7109375" style="3" customWidth="1"/>
@@ -55618,10 +55618,9 @@
     <col min="57" max="57" width="34.7109375" style="3" customWidth="1"/>
     <col min="58" max="58" width="48.7109375" style="3" customWidth="1"/>
     <col min="59" max="59" width="40.7109375" customWidth="1"/>
-    <col min="60" max="60" width="10.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" hidden="1">
+    <row r="1" spans="1:59" hidden="1">
       <c r="A1" s="6" t="s">
         <v>2232</v>
       </c>
@@ -55799,11 +55798,8 @@
       <c r="BG1" s="1" t="s">
         <v>2118</v>
       </c>
-      <c r="BH1" s="1" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="2" spans="1:60" hidden="1">
+    </row>
+    <row r="2" spans="1:59" hidden="1">
       <c r="A2" s="7" t="s">
         <v>2233</v>
       </c>
@@ -55891,11 +55887,8 @@
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
-      <c r="BH2" s="1" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60" hidden="1">
+    </row>
+    <row r="3" spans="1:59" hidden="1">
       <c r="A3" s="7" t="s">
         <v>2233</v>
       </c>
@@ -56010,7 +56003,7 @@
       </c>
       <c r="BG3" s="1"/>
     </row>
-    <row r="4" spans="1:60" hidden="1">
+    <row r="4" spans="1:59" hidden="1">
       <c r="E4" s="7" t="s">
         <v>2122</v>
       </c>
@@ -56093,7 +56086,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="5" spans="1:60" hidden="1">
+    <row r="5" spans="1:59" hidden="1">
       <c r="K5" s="7" t="s">
         <v>2250</v>
       </c>
@@ -56146,7 +56139,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="6" spans="1:60">
+    <row r="6" spans="1:59">
       <c r="A6" s="6" t="s">
         <v>2232</v>
       </c>
@@ -56323,9 +56316,6 @@
       </c>
       <c r="BG6" s="1" t="s">
         <v>2118</v>
-      </c>
-      <c r="BH6" s="1" t="s">
-        <v>2241</v>
       </c>
     </row>
   </sheetData>

--- a/templates/oefen/oefen_geologie_template.xlsx
+++ b/templates/oefen/oefen_geologie_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15192" uniqueCount="2546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15196" uniqueCount="2548">
   <si>
     <t>identificatie</t>
   </si>
@@ -7289,6 +7289,12 @@
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bam</t>
   </si>
   <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbb</t>
+  </si>
+  <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbo</t>
+  </si>
+  <si>
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/boc</t>
   </si>
   <si>
@@ -7628,13 +7634,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-03-31 16:51:51.468547</t>
+    <t>2026-05-06 16:21:34.263173</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.3.1</t>
   </si>
   <si>
     <t>xdov-version</t>
@@ -8033,7 +8039,7 @@
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="Table33" displayName="Table33" ref="BM3:BN12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="Table33" displayName="Table33" ref="BM3:BN14" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Beschrijving"/>
@@ -8591,7 +8597,7 @@
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
       <c r="BG1" s="1" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
@@ -8775,15 +8781,15 @@
       </c>
       <c r="BT2" s="1"/>
       <c r="BU2" s="1" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="BV2" s="1"/>
       <c r="BW2" s="1" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="BX2" s="1"/>
       <c r="BY2" s="1" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="BZ2" s="1"/>
       <c r="CA2" s="1" t="s">
@@ -8803,11 +8809,11 @@
       </c>
       <c r="CH2" s="1"/>
       <c r="CI2" s="1" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="CJ2" s="1"/>
       <c r="CK2" s="1" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="CL2" s="1"/>
       <c r="CM2" s="1" t="s">
@@ -9293,13 +9299,13 @@
         <v>59</v>
       </c>
       <c r="BO4" s="2" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="BP4" t="s">
         <v>59</v>
       </c>
       <c r="BQ4" s="2" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="BR4" t="s">
         <v>59</v>
@@ -9347,7 +9353,7 @@
         <v>59</v>
       </c>
       <c r="CG4" s="2" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="CH4" t="s">
         <v>59</v>
@@ -9571,13 +9577,13 @@
         <v>59</v>
       </c>
       <c r="BO5" s="2" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="BP5" t="s">
         <v>59</v>
       </c>
       <c r="BQ5" s="2" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="BR5" t="s">
         <v>59</v>
@@ -9625,7 +9631,7 @@
         <v>59</v>
       </c>
       <c r="CG5" s="2" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="CH5" t="s">
         <v>59</v>
@@ -9837,13 +9843,13 @@
         <v>59</v>
       </c>
       <c r="BO6" s="2" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="BP6" t="s">
         <v>59</v>
       </c>
       <c r="BQ6" s="2" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="BR6" t="s">
         <v>59</v>
@@ -9891,7 +9897,7 @@
         <v>59</v>
       </c>
       <c r="CG6" s="2" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="CH6" t="s">
         <v>59</v>
@@ -10073,7 +10079,7 @@
         <v>59</v>
       </c>
       <c r="BO7" s="2" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="BP7" t="s">
         <v>59</v>
@@ -10291,7 +10297,7 @@
         <v>59</v>
       </c>
       <c r="BO8" s="2" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="BP8" t="s">
         <v>59</v>
@@ -10491,7 +10497,7 @@
         <v>59</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="BP9" t="s">
         <v>59</v>
@@ -10679,7 +10685,7 @@
         <v>59</v>
       </c>
       <c r="BO10" s="2" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="BP10" t="s">
         <v>59</v>
@@ -10867,7 +10873,7 @@
         <v>59</v>
       </c>
       <c r="BO11" s="2" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="BP11" t="s">
         <v>59</v>
@@ -11049,7 +11055,7 @@
         <v>59</v>
       </c>
       <c r="BO12" s="2" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="BP12" t="s">
         <v>59</v>
@@ -11224,8 +11230,14 @@
       <c r="BL13" t="s">
         <v>59</v>
       </c>
+      <c r="BM13" s="2" t="s">
+        <v>2427</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>59</v>
+      </c>
       <c r="BO13" s="2" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="BP13" t="s">
         <v>59</v>
@@ -11400,8 +11412,14 @@
       <c r="BL14" t="s">
         <v>59</v>
       </c>
+      <c r="BM14" s="2" t="s">
+        <v>2428</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>59</v>
+      </c>
       <c r="BO14" s="2" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="BP14" t="s">
         <v>59</v>
@@ -11577,7 +11595,7 @@
         <v>59</v>
       </c>
       <c r="BO15" s="2" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="BP15" t="s">
         <v>59</v>
@@ -11753,7 +11771,7 @@
         <v>59</v>
       </c>
       <c r="BO16" s="2" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="BP16" t="s">
         <v>59</v>
@@ -11929,7 +11947,7 @@
         <v>59</v>
       </c>
       <c r="BO17" s="2" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="BP17" t="s">
         <v>59</v>
@@ -12099,7 +12117,7 @@
         <v>59</v>
       </c>
       <c r="BO18" s="2" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="BP18" t="s">
         <v>59</v>
@@ -12263,7 +12281,7 @@
         <v>59</v>
       </c>
       <c r="BO19" s="2" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="BP19" t="s">
         <v>59</v>
@@ -12427,7 +12445,7 @@
         <v>59</v>
       </c>
       <c r="BO20" s="2" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="BP20" t="s">
         <v>59</v>
@@ -12591,7 +12609,7 @@
         <v>59</v>
       </c>
       <c r="BO21" s="2" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="BP21" t="s">
         <v>59</v>
@@ -12755,7 +12773,7 @@
         <v>59</v>
       </c>
       <c r="BO22" s="2" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="BP22" t="s">
         <v>59</v>
@@ -12919,7 +12937,7 @@
         <v>59</v>
       </c>
       <c r="BO23" s="2" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="BP23" t="s">
         <v>59</v>
@@ -13077,7 +13095,7 @@
         <v>59</v>
       </c>
       <c r="BO24" s="2" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="BP24" t="s">
         <v>59</v>
@@ -13235,7 +13253,7 @@
         <v>59</v>
       </c>
       <c r="BO25" s="2" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="BP25" t="s">
         <v>59</v>
@@ -13393,7 +13411,7 @@
         <v>59</v>
       </c>
       <c r="BO26" s="2" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="BP26" t="s">
         <v>59</v>
@@ -13551,7 +13569,7 @@
         <v>59</v>
       </c>
       <c r="BO27" s="2" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="BP27" t="s">
         <v>59</v>
@@ -13709,7 +13727,7 @@
         <v>59</v>
       </c>
       <c r="BO28" s="2" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="BP28" t="s">
         <v>59</v>
@@ -13867,7 +13885,7 @@
         <v>59</v>
       </c>
       <c r="BO29" s="2" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="BP29" t="s">
         <v>59</v>
@@ -14019,7 +14037,7 @@
         <v>59</v>
       </c>
       <c r="BO30" s="2" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="BP30" t="s">
         <v>59</v>
@@ -14159,7 +14177,7 @@
         <v>59</v>
       </c>
       <c r="BO31" s="2" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="BP31" t="s">
         <v>59</v>
@@ -14299,7 +14317,7 @@
         <v>59</v>
       </c>
       <c r="BO32" s="2" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="BP32" t="s">
         <v>59</v>
@@ -14439,7 +14457,7 @@
         <v>59</v>
       </c>
       <c r="BO33" s="2" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="BP33" t="s">
         <v>59</v>
@@ -14579,7 +14597,7 @@
         <v>59</v>
       </c>
       <c r="BO34" s="2" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="BP34" t="s">
         <v>59</v>
@@ -14719,7 +14737,7 @@
         <v>59</v>
       </c>
       <c r="BO35" s="2" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="BP35" t="s">
         <v>59</v>
@@ -14859,7 +14877,7 @@
         <v>59</v>
       </c>
       <c r="BO36" s="2" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="BP36" t="s">
         <v>59</v>
@@ -14999,7 +15017,7 @@
         <v>59</v>
       </c>
       <c r="BO37" s="2" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="BP37" t="s">
         <v>59</v>
@@ -15139,7 +15157,7 @@
         <v>59</v>
       </c>
       <c r="BO38" s="2" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="BP38" t="s">
         <v>59</v>
@@ -15279,7 +15297,7 @@
         <v>59</v>
       </c>
       <c r="BO39" s="2" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="BP39" t="s">
         <v>59</v>
@@ -15419,7 +15437,7 @@
         <v>59</v>
       </c>
       <c r="BO40" s="2" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="BP40" t="s">
         <v>59</v>
@@ -53947,113 +53965,113 @@
     <hyperlink ref="BM12" r:id="rId32"/>
     <hyperlink ref="BO12" r:id="rId33"/>
     <hyperlink ref="BK13" r:id="rId34"/>
-    <hyperlink ref="BO13" r:id="rId35"/>
-    <hyperlink ref="BK14" r:id="rId36"/>
-    <hyperlink ref="BO14" r:id="rId37"/>
-    <hyperlink ref="BK15" r:id="rId38"/>
-    <hyperlink ref="BO15" r:id="rId39"/>
-    <hyperlink ref="BK16" r:id="rId40"/>
-    <hyperlink ref="BO16" r:id="rId41"/>
-    <hyperlink ref="BK17" r:id="rId42"/>
-    <hyperlink ref="BO17" r:id="rId43"/>
-    <hyperlink ref="BK18" r:id="rId44"/>
-    <hyperlink ref="BO18" r:id="rId45"/>
-    <hyperlink ref="BK19" r:id="rId46"/>
-    <hyperlink ref="BO19" r:id="rId47"/>
-    <hyperlink ref="BK20" r:id="rId48"/>
-    <hyperlink ref="BO20" r:id="rId49"/>
-    <hyperlink ref="BK21" r:id="rId50"/>
-    <hyperlink ref="BO21" r:id="rId51"/>
-    <hyperlink ref="BK22" r:id="rId52"/>
-    <hyperlink ref="BO22" r:id="rId53"/>
-    <hyperlink ref="BK23" r:id="rId54"/>
-    <hyperlink ref="BO23" r:id="rId55"/>
-    <hyperlink ref="BK24" r:id="rId56"/>
-    <hyperlink ref="BO24" r:id="rId57"/>
-    <hyperlink ref="BK25" r:id="rId58"/>
-    <hyperlink ref="BO25" r:id="rId59"/>
-    <hyperlink ref="BK26" r:id="rId60"/>
-    <hyperlink ref="BO26" r:id="rId61"/>
-    <hyperlink ref="BK27" r:id="rId62"/>
-    <hyperlink ref="BO27" r:id="rId63"/>
-    <hyperlink ref="BK28" r:id="rId64"/>
-    <hyperlink ref="BO28" r:id="rId65"/>
-    <hyperlink ref="BK29" r:id="rId66"/>
-    <hyperlink ref="BO29" r:id="rId67"/>
-    <hyperlink ref="BK30" r:id="rId68"/>
-    <hyperlink ref="BO30" r:id="rId69"/>
-    <hyperlink ref="BK31" r:id="rId70"/>
-    <hyperlink ref="BO31" r:id="rId71"/>
-    <hyperlink ref="BK32" r:id="rId72"/>
-    <hyperlink ref="BO32" r:id="rId73"/>
-    <hyperlink ref="BK33" r:id="rId74"/>
-    <hyperlink ref="BO33" r:id="rId75"/>
-    <hyperlink ref="BK34" r:id="rId76"/>
-    <hyperlink ref="BO34" r:id="rId77"/>
-    <hyperlink ref="BK35" r:id="rId78"/>
-    <hyperlink ref="BO35" r:id="rId79"/>
-    <hyperlink ref="BK36" r:id="rId80"/>
-    <hyperlink ref="BO36" r:id="rId81"/>
-    <hyperlink ref="BK37" r:id="rId82"/>
-    <hyperlink ref="BO37" r:id="rId83"/>
-    <hyperlink ref="BK38" r:id="rId84"/>
-    <hyperlink ref="BO38" r:id="rId85"/>
-    <hyperlink ref="BK39" r:id="rId86"/>
-    <hyperlink ref="BO39" r:id="rId87"/>
-    <hyperlink ref="BK40" r:id="rId88"/>
-    <hyperlink ref="BO40" r:id="rId89"/>
-    <hyperlink ref="BK41" r:id="rId90"/>
-    <hyperlink ref="BK42" r:id="rId91"/>
-    <hyperlink ref="BK43" r:id="rId92"/>
-    <hyperlink ref="BK44" r:id="rId93"/>
-    <hyperlink ref="BK45" r:id="rId94"/>
-    <hyperlink ref="BK46" r:id="rId95"/>
-    <hyperlink ref="BK47" r:id="rId96"/>
-    <hyperlink ref="BK48" r:id="rId97"/>
-    <hyperlink ref="BK49" r:id="rId98"/>
-    <hyperlink ref="BK50" r:id="rId99"/>
-    <hyperlink ref="BK51" r:id="rId100"/>
-    <hyperlink ref="BK52" r:id="rId101"/>
-    <hyperlink ref="BK53" r:id="rId102"/>
-    <hyperlink ref="BK54" r:id="rId103"/>
-    <hyperlink ref="BK55" r:id="rId104"/>
-    <hyperlink ref="BK56" r:id="rId105"/>
-    <hyperlink ref="BK57" r:id="rId106"/>
-    <hyperlink ref="BK58" r:id="rId107"/>
-    <hyperlink ref="BK59" r:id="rId108"/>
-    <hyperlink ref="BK60" r:id="rId109"/>
-    <hyperlink ref="BK61" r:id="rId110"/>
-    <hyperlink ref="BK62" r:id="rId111"/>
-    <hyperlink ref="BK63" r:id="rId112"/>
-    <hyperlink ref="BK64" r:id="rId113"/>
-    <hyperlink ref="BK65" r:id="rId114"/>
-    <hyperlink ref="BK66" r:id="rId115"/>
-    <hyperlink ref="BK67" r:id="rId116"/>
-    <hyperlink ref="BK68" r:id="rId117"/>
-    <hyperlink ref="BK69" r:id="rId118"/>
-    <hyperlink ref="BK70" r:id="rId119"/>
-    <hyperlink ref="BK71" r:id="rId120"/>
-    <hyperlink ref="BK72" r:id="rId121"/>
-    <hyperlink ref="BK73" r:id="rId122"/>
-    <hyperlink ref="BK74" r:id="rId123"/>
-    <hyperlink ref="BK75" r:id="rId124"/>
-    <hyperlink ref="BK76" r:id="rId125"/>
-    <hyperlink ref="BK77" r:id="rId126"/>
-    <hyperlink ref="BK78" r:id="rId127"/>
-    <hyperlink ref="BK79" r:id="rId128"/>
-    <hyperlink ref="BK80" r:id="rId129"/>
-    <hyperlink ref="BK81" r:id="rId130"/>
-    <hyperlink ref="BK82" r:id="rId131"/>
-    <hyperlink ref="BK83" r:id="rId132"/>
-    <hyperlink ref="BK84" r:id="rId133"/>
-    <hyperlink ref="BK85" r:id="rId134"/>
-    <hyperlink ref="BK86" r:id="rId135"/>
-    <hyperlink ref="BK87" r:id="rId136"/>
+    <hyperlink ref="BM13" r:id="rId35"/>
+    <hyperlink ref="BO13" r:id="rId36"/>
+    <hyperlink ref="BK14" r:id="rId37"/>
+    <hyperlink ref="BM14" r:id="rId38"/>
+    <hyperlink ref="BO14" r:id="rId39"/>
+    <hyperlink ref="BK15" r:id="rId40"/>
+    <hyperlink ref="BO15" r:id="rId41"/>
+    <hyperlink ref="BK16" r:id="rId42"/>
+    <hyperlink ref="BO16" r:id="rId43"/>
+    <hyperlink ref="BK17" r:id="rId44"/>
+    <hyperlink ref="BO17" r:id="rId45"/>
+    <hyperlink ref="BK18" r:id="rId46"/>
+    <hyperlink ref="BO18" r:id="rId47"/>
+    <hyperlink ref="BK19" r:id="rId48"/>
+    <hyperlink ref="BO19" r:id="rId49"/>
+    <hyperlink ref="BK20" r:id="rId50"/>
+    <hyperlink ref="BO20" r:id="rId51"/>
+    <hyperlink ref="BK21" r:id="rId52"/>
+    <hyperlink ref="BO21" r:id="rId53"/>
+    <hyperlink ref="BK22" r:id="rId54"/>
+    <hyperlink ref="BO22" r:id="rId55"/>
+    <hyperlink ref="BK23" r:id="rId56"/>
+    <hyperlink ref="BO23" r:id="rId57"/>
+    <hyperlink ref="BK24" r:id="rId58"/>
+    <hyperlink ref="BO24" r:id="rId59"/>
+    <hyperlink ref="BK25" r:id="rId60"/>
+    <hyperlink ref="BO25" r:id="rId61"/>
+    <hyperlink ref="BK26" r:id="rId62"/>
+    <hyperlink ref="BO26" r:id="rId63"/>
+    <hyperlink ref="BK27" r:id="rId64"/>
+    <hyperlink ref="BO27" r:id="rId65"/>
+    <hyperlink ref="BK28" r:id="rId66"/>
+    <hyperlink ref="BO28" r:id="rId67"/>
+    <hyperlink ref="BK29" r:id="rId68"/>
+    <hyperlink ref="BO29" r:id="rId69"/>
+    <hyperlink ref="BK30" r:id="rId70"/>
+    <hyperlink ref="BO30" r:id="rId71"/>
+    <hyperlink ref="BK31" r:id="rId72"/>
+    <hyperlink ref="BO31" r:id="rId73"/>
+    <hyperlink ref="BK32" r:id="rId74"/>
+    <hyperlink ref="BO32" r:id="rId75"/>
+    <hyperlink ref="BK33" r:id="rId76"/>
+    <hyperlink ref="BO33" r:id="rId77"/>
+    <hyperlink ref="BK34" r:id="rId78"/>
+    <hyperlink ref="BO34" r:id="rId79"/>
+    <hyperlink ref="BK35" r:id="rId80"/>
+    <hyperlink ref="BO35" r:id="rId81"/>
+    <hyperlink ref="BK36" r:id="rId82"/>
+    <hyperlink ref="BO36" r:id="rId83"/>
+    <hyperlink ref="BK37" r:id="rId84"/>
+    <hyperlink ref="BO37" r:id="rId85"/>
+    <hyperlink ref="BK38" r:id="rId86"/>
+    <hyperlink ref="BO38" r:id="rId87"/>
+    <hyperlink ref="BK39" r:id="rId88"/>
+    <hyperlink ref="BO39" r:id="rId89"/>
+    <hyperlink ref="BK40" r:id="rId90"/>
+    <hyperlink ref="BO40" r:id="rId91"/>
+    <hyperlink ref="BK41" r:id="rId92"/>
+    <hyperlink ref="BK42" r:id="rId93"/>
+    <hyperlink ref="BK43" r:id="rId94"/>
+    <hyperlink ref="BK44" r:id="rId95"/>
+    <hyperlink ref="BK45" r:id="rId96"/>
+    <hyperlink ref="BK46" r:id="rId97"/>
+    <hyperlink ref="BK47" r:id="rId98"/>
+    <hyperlink ref="BK48" r:id="rId99"/>
+    <hyperlink ref="BK49" r:id="rId100"/>
+    <hyperlink ref="BK50" r:id="rId101"/>
+    <hyperlink ref="BK51" r:id="rId102"/>
+    <hyperlink ref="BK52" r:id="rId103"/>
+    <hyperlink ref="BK53" r:id="rId104"/>
+    <hyperlink ref="BK54" r:id="rId105"/>
+    <hyperlink ref="BK55" r:id="rId106"/>
+    <hyperlink ref="BK56" r:id="rId107"/>
+    <hyperlink ref="BK57" r:id="rId108"/>
+    <hyperlink ref="BK58" r:id="rId109"/>
+    <hyperlink ref="BK59" r:id="rId110"/>
+    <hyperlink ref="BK60" r:id="rId111"/>
+    <hyperlink ref="BK61" r:id="rId112"/>
+    <hyperlink ref="BK62" r:id="rId113"/>
+    <hyperlink ref="BK63" r:id="rId114"/>
+    <hyperlink ref="BK64" r:id="rId115"/>
+    <hyperlink ref="BK65" r:id="rId116"/>
+    <hyperlink ref="BK66" r:id="rId117"/>
+    <hyperlink ref="BK67" r:id="rId118"/>
+    <hyperlink ref="BK68" r:id="rId119"/>
+    <hyperlink ref="BK69" r:id="rId120"/>
+    <hyperlink ref="BK70" r:id="rId121"/>
+    <hyperlink ref="BK71" r:id="rId122"/>
+    <hyperlink ref="BK72" r:id="rId123"/>
+    <hyperlink ref="BK73" r:id="rId124"/>
+    <hyperlink ref="BK74" r:id="rId125"/>
+    <hyperlink ref="BK75" r:id="rId126"/>
+    <hyperlink ref="BK76" r:id="rId127"/>
+    <hyperlink ref="BK77" r:id="rId128"/>
+    <hyperlink ref="BK78" r:id="rId129"/>
+    <hyperlink ref="BK79" r:id="rId130"/>
+    <hyperlink ref="BK80" r:id="rId131"/>
+    <hyperlink ref="BK81" r:id="rId132"/>
+    <hyperlink ref="BK82" r:id="rId133"/>
+    <hyperlink ref="BK83" r:id="rId134"/>
+    <hyperlink ref="BK84" r:id="rId135"/>
+    <hyperlink ref="BK85" r:id="rId136"/>
+    <hyperlink ref="BK86" r:id="rId137"/>
+    <hyperlink ref="BK87" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="46">
-    <tablePart r:id="rId137"/>
-    <tablePart r:id="rId138"/>
     <tablePart r:id="rId139"/>
     <tablePart r:id="rId140"/>
     <tablePart r:id="rId141"/>
@@ -54098,6 +54116,8 @@
     <tablePart r:id="rId180"/>
     <tablePart r:id="rId181"/>
     <tablePart r:id="rId182"/>
+    <tablePart r:id="rId183"/>
+    <tablePart r:id="rId184"/>
   </tableParts>
 </worksheet>
 </file>
@@ -56356,7 +56376,7 @@
       <formula1>'Codelijsten'!$BK$4:$BK$87</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:I1000001">
-      <formula1>'Codelijsten'!$BM$4:$BM$12</formula1>
+      <formula1>'Codelijsten'!$BM$4:$BM$14</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T7:T1000001">
       <formula1>-146096</formula1>
@@ -56477,55 +56497,55 @@
   <sheetData>
     <row r="1" spans="1:73" hidden="1">
       <c r="A1" s="6" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2121</v>
@@ -56534,16 +56554,16 @@
         <v>2123</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>1</v>
@@ -56552,7 +56572,7 @@
         <v>2</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>763</v>
@@ -56567,82 +56587,82 @@
         <v>1849</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="BE1" s="1" t="s">
         <v>2300</v>
@@ -56723,7 +56743,7 @@
       </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -56735,7 +56755,7 @@
         <v>2</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>763</v>
@@ -56750,7 +56770,7 @@
         <v>1849</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="AF2" s="1" t="s">
         <v>43</v>
@@ -56783,7 +56803,7 @@
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="BC2" s="1"/>
       <c r="BD2" s="1"/>
@@ -56822,7 +56842,7 @@
         <v>757</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -56835,7 +56855,7 @@
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
       <c r="O3" s="7" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
@@ -56863,7 +56883,7 @@
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
@@ -56895,10 +56915,10 @@
         <v>763</v>
       </c>
       <c r="BB3" s="7" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="BC3" s="7" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="BD3" s="1" t="s">
         <v>57</v>
@@ -56942,13 +56962,13 @@
     </row>
     <row r="4" spans="1:73" hidden="1">
       <c r="D4" s="7" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -56957,13 +56977,13 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="1" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
@@ -57054,7 +57074,7 @@
         <v>767</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>769</v>
@@ -57083,13 +57103,13 @@
     </row>
     <row r="6" spans="1:73" hidden="1">
       <c r="F6" s="7" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>775</v>
@@ -57106,55 +57126,55 @@
     </row>
     <row r="7" spans="1:73">
       <c r="A7" s="6" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>2121</v>
@@ -57163,16 +57183,16 @@
         <v>2123</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="X7" s="1" t="s">
         <v>1</v>
@@ -57181,7 +57201,7 @@
         <v>2</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="AA7" s="1" t="s">
         <v>763</v>
@@ -57196,82 +57216,82 @@
         <v>1849</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="AF7" s="1" t="s">
         <v>43</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="AY7" s="1" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="BA7" s="1" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="BB7" s="1" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="BE7" s="1" t="s">
         <v>2300</v>
@@ -57422,50 +57442,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="B1" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="B2" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="B3" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="B4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="B5" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="B6" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
     </row>
   </sheetData>

--- a/templates/oefen/oefen_geologie_template.xlsx
+++ b/templates/oefen/oefen_geologie_template.xlsx
@@ -7634,19 +7634,19 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-06 16:21:34.263173</t>
+    <t>2026-05-19 11:29:07.807093</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.1</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>10.1.0</t>
+    <t>10.2.0</t>
   </si>
   <si>
     <t>schema-version</t>

--- a/templates/oefen/oefen_geologie_template.xlsx
+++ b/templates/oefen/oefen_geologie_template.xlsx
@@ -7634,13 +7634,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:29:07.807093</t>
+    <t>2026-05-19 14:52:58.853188</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
